--- a/tools/importer/reports/import-accounts.report.xlsx
+++ b/tools/importer/reports/import-accounts.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>index.report.json</t>
+  </si>
+  <si>
+    <t>["tabs-panel","hero-promo","hero-promo","hero-promo","carousel-banner","carousel-banner","columns-split","columns-split","columns-split","columns-split","columns-split","columns-split","columns-split","cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","widget","cards-stats","cards-stats"]</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>2026-09-09T15:24:08.457Z</t>
+  </si>
+  <si>
+    <t>Personal Banking | Internet Banking | Corporate, NRI Banking Services Online - Axis Bank</t>
+  </si>
+  <si>
+    <t>https://www.axis.bank.in/</t>
+  </si>
+  <si>
     <t>accounts/savings-account.report.json</t>
   </si>
   <si>
@@ -46,13 +70,10 @@
     <t>accounts/savings-account</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>accounts</t>
   </si>
   <si>
-    <t>2026-09-09T07:29:09.461Z</t>
+    <t>2026-09-09T15:24:53.332Z</t>
   </si>
   <si>
     <t>Savings Account - Open Bank Account Online in Minutes | Axis Bank</t>
@@ -70,13 +91,55 @@
     <t>cards/credit-card</t>
   </si>
   <si>
-    <t>2026-09-09T07:22:17.841Z</t>
+    <t>2026-09-09T15:25:05.275Z</t>
   </si>
   <si>
     <t>Credit Card - Apply for Credit Card Online &amp; Get Instant Approval | Axis Bank</t>
   </si>
   <si>
     <t>https://www.axis.bank.in/cards/credit-card</t>
+  </si>
+  <si>
+    <t>deposits/fixed-deposits.report.json</t>
+  </si>
+  <si>
+    <t>["columns-split","columns-split","carousel-banner","cards-product","cards-product","cards-product","cards-product","widget","hero-promo","hero-promo","hero-promo","tabs-panel","tabs-panel","accordion-faq","accordion-faq"]</t>
+  </si>
+  <si>
+    <t>deposits/fixed-deposits</t>
+  </si>
+  <si>
+    <t>deposits</t>
+  </si>
+  <si>
+    <t>2026-09-09T10:19:27.613Z</t>
+  </si>
+  <si>
+    <t>Fixed Deposits – Open FD at Attractive Interest Rates | Axis Bank</t>
+  </si>
+  <si>
+    <t>https://www.axis.bank.in/deposits/fixed-deposits</t>
+  </si>
+  <si>
+    <t>loans/home-loan.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product"]</t>
+  </si>
+  <si>
+    <t>loans/home-loan</t>
+  </si>
+  <si>
+    <t>loans</t>
+  </si>
+  <si>
+    <t>2026-09-09T10:36:24.881Z</t>
+  </si>
+  <si>
+    <t>Builder Buyer Agreement (BBA)</t>
+  </si>
+  <si>
+    <t>https://www.axis.bank.in/loans/home-loan</t>
   </si>
 </sst>
 </file>
@@ -465,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -542,16 +605,94 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
